--- a/data/MACC_Model_Assumptions_v2_Korean.xlsx
+++ b/data/MACC_Model_Assumptions_v2_Korean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jinsupark/jinsu-coding/petrochemical_macc_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEEEC52-8F6C-8444-BBF9-5F739255161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6859600C-0902-F24B-8F0B-805138EFF515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="500" windowWidth="37400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model_Parameters" sheetId="2" r:id="rId1"/>
@@ -23,12 +23,25 @@
     <sheet name="Baseline_Emissions" sheetId="9" r:id="rId8"/>
     <sheet name="Facility_Applicability" sheetId="10" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="174">
   <si>
     <t>parameter</t>
   </si>
@@ -144,12 +157,6 @@
     <t>re_lifecycle_emission_factor</t>
   </si>
   <si>
-    <t>재생에너지 생애주기 배출</t>
-  </si>
-  <si>
-    <t>재생에너지 생애주기 배출 문헌</t>
-  </si>
-  <si>
     <t>h2_lower_heating_value</t>
   </si>
   <si>
@@ -378,9 +385,6 @@
     <t>그린수소</t>
   </si>
   <si>
-    <t>그린수소 (재생에너지 전해, 생애주기)</t>
-  </si>
-  <si>
     <t>Grid_Electricity</t>
   </si>
   <si>
@@ -556,6 +560,9 @@
   </si>
   <si>
     <t xml:space="preserve">납사 연료 연소 </t>
+  </si>
+  <si>
+    <t>재생에너지</t>
   </si>
 </sst>
 </file>
@@ -622,6 +629,369 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2882900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF5A2A5E-9B1F-584B-93B2-0741F1A9B629}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="3657600"/>
+          <a:ext cx="3721100" cy="1117600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>열 효율계수 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>에너지사용량 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t> 생산량</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t> 온실가스량 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>-&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t> 각 에너지원별 에너지집약도</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t> 온실가스 배출량</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63ACFF40-A751-D64A-9221-70AB45E70B01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3924300" y="5562600"/>
+          <a:ext cx="3721100" cy="863600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>수소가격 더블체크 필요</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B868C0F-DE2D-214E-B202-E8504F636539}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2324100" y="6096000"/>
+          <a:ext cx="3721100" cy="863600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>재생에너지 가격 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>PPA </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>가격을 쓸 것인지</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>?</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>LCOE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>전망을 쓸 것인지</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>?</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8850C23B-3F2C-814F-9F93-C5D5C7474076}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2628900" y="5676900"/>
+          <a:ext cx="3721100" cy="863600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>전력가격은 상승으로 가정해야 하나</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>?</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1110,88 +1480,86 @@
         <v>37</v>
       </c>
       <c r="B12">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>120</v>
       </c>
       <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
         <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0.18</v>
       </c>
       <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
         <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
         <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1202,68 +1570,70 @@
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="60.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1296,18 +1666,18 @@
         <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
         <v>76</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
       </c>
       <c r="E3">
         <v>0.18</v>
@@ -1340,18 +1710,18 @@
         <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1384,18 +1754,18 @@
         <v>25</v>
       </c>
       <c r="P4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
         <v>83</v>
-      </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1422,7 +1792,7 @@
         <v>99</v>
       </c>
       <c r="P5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1656,6 +2026,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1672,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1885,6 +2256,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1901,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2114,6 +2486,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2130,7 +2503,7 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2360,156 +2733,153 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>92</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>93</v>
       </c>
-      <c r="D1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" t="s">
-        <v>95</v>
-      </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C2">
         <v>5.4199999999999998E-2</v>
       </c>
       <c r="F2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C3">
         <v>1.49E-2</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4">
         <v>1.49E-2</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5">
         <v>1.49E-2</v>
       </c>
       <c r="F5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>1.49E-2</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7">
         <v>1.49E-2</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>1.49E-2</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D10">
         <v>0.45</v>
       </c>
       <c r="F10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2527,34 +2897,34 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>123</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>124</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>126</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>127</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>128</v>
-      </c>
-      <c r="H1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J1" t="s">
-        <v>131</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -2562,16 +2932,16 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" t="s">
         <v>132</v>
-      </c>
-      <c r="B2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D2" t="s">
-        <v>135</v>
       </c>
       <c r="E2">
         <v>29</v>
@@ -2592,21 +2962,21 @@
         <v>1.7390000000000001</v>
       </c>
       <c r="K2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E3">
         <v>25.39</v>
@@ -2627,21 +2997,21 @@
         <v>1.53</v>
       </c>
       <c r="K3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -2662,7 +3032,7 @@
         <v>1.73</v>
       </c>
       <c r="K4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2677,60 +3047,60 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" t="s">
         <v>143</v>
       </c>
-      <c r="B1" t="s">
+      <c r="I1" t="s">
         <v>144</v>
       </c>
-      <c r="C1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>145</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>146</v>
       </c>
-      <c r="I1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K1" t="s">
-        <v>149</v>
-      </c>
       <c r="L1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -2745,30 +3115,30 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -2783,30 +3153,30 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -2821,30 +3191,30 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" t="s">
         <v>155</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>156</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>157</v>
-      </c>
-      <c r="D5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" t="s">
-        <v>160</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -2859,30 +3229,30 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" t="s">
         <v>156</v>
       </c>
-      <c r="C6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" t="s">
-        <v>159</v>
-      </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -2897,30 +3267,30 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" t="s">
         <v>156</v>
       </c>
-      <c r="C7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" t="s">
-        <v>159</v>
-      </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -2935,30 +3305,30 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" t="s">
         <v>167</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>168</v>
-      </c>
-      <c r="C8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" t="s">
-        <v>171</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -2973,30 +3343,30 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" t="s">
         <v>167</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>168</v>
-      </c>
-      <c r="C9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" t="s">
-        <v>171</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -3011,30 +3381,30 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" t="s">
         <v>167</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>168</v>
-      </c>
-      <c r="C10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" t="s">
-        <v>171</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -3049,10 +3419,10 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
